--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20232.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -101,33 +101,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>VASQUEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>MARGARITA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
 </sst>
 </file>
@@ -853,16 +826,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>56</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -876,16 +852,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>89.73999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -899,16 +878,19 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -922,16 +904,19 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>92.11</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -945,16 +930,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H6">
+        <v>5.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -968,16 +956,19 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>79.31</v>
+      </c>
+      <c r="H7">
+        <v>5.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -991,16 +982,19 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>91.3</v>
+      </c>
+      <c r="H8">
+        <v>6.4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1014,16 +1008,19 @@
         <v>33</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>84.84999999999999</v>
+      </c>
+      <c r="H9">
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1037,16 +1034,19 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H10">
+        <v>6.6</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1060,16 +1060,19 @@
         <v>15</v>
       </c>
       <c r="D11">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>93.33</v>
+      </c>
+      <c r="H11">
+        <v>8.1</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1083,16 +1086,19 @@
         <v>14</v>
       </c>
       <c r="D12">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H12">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -1148,16 +1154,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1174,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>82.05</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1200,16 +1206,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>70.83</v>
+        <v>75</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1226,16 +1232,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>89.47</v>
+        <v>92.11</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1252,16 +1258,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>33.33</v>
+        <v>80</v>
       </c>
       <c r="H6">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1278,16 +1284,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G7">
-        <v>55.17</v>
+        <v>79.31</v>
       </c>
       <c r="H7">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1304,16 +1310,16 @@
         <v>0</v>
       </c>
       <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>21</v>
+      </c>
+      <c r="G8">
+        <v>91.3</v>
+      </c>
+      <c r="H8">
         <v>7</v>
-      </c>
-      <c r="F8">
-        <v>16</v>
-      </c>
-      <c r="G8">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="H8">
-        <v>6.4</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1339,7 +1345,7 @@
         <v>84.84999999999999</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1356,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="H10">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1391,7 +1397,7 @@
         <v>93.33</v>
       </c>
       <c r="H11">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1417,7 +1423,7 @@
         <v>92.86</v>
       </c>
       <c r="H12">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -1427,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1457,75 +1463,6 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920180</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920112</v>
-      </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920348</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20232.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20232.xlsx
@@ -758,7 +758,7 @@
         <v>21</v>
       </c>
       <c r="C12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -767,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="H12">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1083,7 +1083,7 @@
         <v>21</v>
       </c>
       <c r="C12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="H12">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1154,16 +1154,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1180,16 +1180,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>89.73999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1206,16 +1206,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>75</v>
+        <v>95.83</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1232,13 +1232,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>92.11</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>8.4</v>
@@ -1258,16 +1258,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>96.67</v>
       </c>
       <c r="H6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1284,16 +1284,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>79.31</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1310,16 +1310,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H8">
-        <v>7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1336,16 +1336,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G9">
-        <v>84.84999999999999</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1362,16 +1362,16 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="H10">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1408,7 +1408,7 @@
         <v>21</v>
       </c>
       <c r="C12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -1417,13 +1417,13 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="H12">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
